--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{30C80E80-864B-4917-947B-01CD2AFC0549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D40D6366-58B5-46A5-B710-2F5CADC8D2B1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{30C80E80-864B-4917-947B-01CD2AFC0549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0593FB7A-B52E-44B5-9FFA-D89AB4A46C4A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E488AD1-879C-4CD8-8F82-F75290C17312}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E488AD1-879C-4CD8-8F82-F75290C17312}"/>
   </bookViews>
   <sheets>
     <sheet name="SType2" sheetId="1" r:id="rId1"/>
@@ -490,52 +490,52 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.0000000000000028E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="G2">
-        <v>1.6000000000000025E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="H2">
-        <v>2.200000000000002E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="I2">
-        <v>2.8000000000000018E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="J2">
-        <v>3.4000000000000016E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="K2">
-        <v>4.0000000000000008E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="L2">
-        <v>4.6000000000000006E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="M2">
-        <v>5.2000000000000005E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="N2">
-        <v>5.8000000000000003E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="O2">
-        <v>6.4000000000000001E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="P2">
-        <v>6.9999999999999993E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="Q2">
-        <v>7.5999999999999984E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="R2">
-        <v>8.199999999999999E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="S2">
-        <v>8.7999999999999981E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="T2">
-        <v>9.3999999999999986E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="U2">
-        <v>9.9999999999999978E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -555,52 +555,52 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.0000000000000028E-2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.6000000000000025E-2</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>2.200000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>2.8000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.4000000000000016E-2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>4.0000000000000008E-2</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>4.6000000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>5.2000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>5.8000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>6.4000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>6.9999999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>7.5999999999999984E-2</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>8.199999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>8.7999999999999981E-2</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>9.3999999999999986E-2</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>9.9999999999999978E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -620,52 +620,52 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1.0000000000000028E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="G4">
-        <v>1.6000000000000025E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="H4">
-        <v>2.200000000000002E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="I4">
-        <v>2.8000000000000018E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="J4">
-        <v>3.4000000000000016E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="K4">
-        <v>4.0000000000000008E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="L4">
-        <v>4.6000000000000006E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="M4">
-        <v>5.2000000000000005E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="N4">
-        <v>5.8000000000000003E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="O4">
-        <v>6.4000000000000001E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="P4">
-        <v>6.9999999999999993E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="Q4">
-        <v>7.5999999999999984E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="R4">
-        <v>8.199999999999999E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="S4">
-        <v>8.7999999999999981E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="T4">
-        <v>9.3999999999999986E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="U4">
-        <v>9.9999999999999978E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -685,52 +685,52 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.0000000000000028E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="G5">
-        <v>1.6000000000000025E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="H5">
-        <v>2.200000000000002E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="I5">
-        <v>2.8000000000000018E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="J5">
-        <v>3.4000000000000016E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="K5">
-        <v>4.0000000000000008E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="L5">
-        <v>4.6000000000000006E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="M5">
-        <v>5.2000000000000005E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="N5">
-        <v>5.8000000000000003E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="O5">
-        <v>6.4000000000000001E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="P5">
-        <v>6.9999999999999993E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="Q5">
-        <v>7.5999999999999984E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="R5">
-        <v>8.199999999999999E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="S5">
-        <v>8.7999999999999981E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="T5">
-        <v>9.3999999999999986E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="U5">
-        <v>9.9999999999999978E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -750,52 +750,52 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1.0000000000000028E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="G6">
-        <v>1.6000000000000025E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="H6">
-        <v>2.200000000000002E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="I6">
-        <v>2.8000000000000018E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="J6">
-        <v>3.4000000000000016E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="K6">
-        <v>4.0000000000000008E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="L6">
-        <v>4.6000000000000006E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="M6">
-        <v>5.2000000000000005E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="N6">
-        <v>5.8000000000000003E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="O6">
-        <v>6.4000000000000001E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="P6">
-        <v>6.9999999999999993E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="Q6">
-        <v>7.5999999999999984E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="R6">
-        <v>8.199999999999999E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="S6">
-        <v>8.7999999999999981E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="T6">
-        <v>9.3999999999999986E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="U6">
-        <v>9.9999999999999978E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -815,52 +815,52 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1.0000000000000028E-2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.6000000000000025E-2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>2.200000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>2.8000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>3.4000000000000016E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>4.0000000000000008E-2</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>4.6000000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>5.2000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>5.8000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>6.4000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>6.9999999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>7.5999999999999984E-2</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>8.199999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>8.7999999999999981E-2</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>9.3999999999999986E-2</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>9.9999999999999978E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
@@ -945,52 +945,52 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1.0000000000000028E-2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1.6000000000000025E-2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>2.200000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>2.8000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>3.4000000000000016E-2</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>4.0000000000000008E-2</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>4.6000000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>5.2000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>5.8000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>6.4000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>6.9999999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>7.5999999999999984E-2</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>8.199999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>8.7999999999999981E-2</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>9.3999999999999986E-2</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>9.9999999999999978E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
@@ -1010,52 +1010,52 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1.0000000000000028E-2</v>
+        <v>3.2000000000000015E-3</v>
       </c>
       <c r="G10">
-        <v>1.6000000000000025E-2</v>
+        <v>4.100266666666668E-3</v>
       </c>
       <c r="H10">
-        <v>2.200000000000002E-2</v>
+        <v>5.0005333333333355E-3</v>
       </c>
       <c r="I10">
-        <v>2.8000000000000018E-2</v>
+        <v>5.9008000000000021E-3</v>
       </c>
       <c r="J10">
-        <v>3.4000000000000016E-2</v>
+        <v>6.8010666666666686E-3</v>
       </c>
       <c r="K10">
-        <v>4.0000000000000008E-2</v>
+        <v>7.7013333333333361E-3</v>
       </c>
       <c r="L10">
-        <v>4.6000000000000006E-2</v>
+        <v>8.6016000000000026E-3</v>
       </c>
       <c r="M10">
-        <v>5.2000000000000005E-2</v>
+        <v>9.5018666666666692E-3</v>
       </c>
       <c r="N10">
-        <v>5.8000000000000003E-2</v>
+        <v>1.0402133333333336E-2</v>
       </c>
       <c r="O10">
-        <v>6.4000000000000001E-2</v>
+        <v>1.1302400000000002E-2</v>
       </c>
       <c r="P10">
-        <v>6.9999999999999993E-2</v>
+        <v>1.2202666666666669E-2</v>
       </c>
       <c r="Q10">
-        <v>7.5999999999999984E-2</v>
+        <v>1.3102933333333337E-2</v>
       </c>
       <c r="R10">
-        <v>8.199999999999999E-2</v>
+        <v>1.4003200000000004E-2</v>
       </c>
       <c r="S10">
-        <v>8.7999999999999981E-2</v>
+        <v>1.490346666666667E-2</v>
       </c>
       <c r="T10">
-        <v>9.3999999999999986E-2</v>
+        <v>1.5803733333333337E-2</v>
       </c>
       <c r="U10">
-        <v>9.9999999999999978E-2</v>
+        <v>1.6704000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">

--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{30C80E80-864B-4917-947B-01CD2AFC0549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0593FB7A-B52E-44B5-9FFA-D89AB4A46C4A}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{30C80E80-864B-4917-947B-01CD2AFC0549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B58BA1-B571-44EE-9DD5-576DDB516A23}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E488AD1-879C-4CD8-8F82-F75290C17312}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E488AD1-879C-4CD8-8F82-F75290C17312}"/>
   </bookViews>
   <sheets>
     <sheet name="SType2" sheetId="1" r:id="rId1"/>
@@ -490,52 +490,52 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>4.0000000000000018E-3</v>
+        <v>8.0000000000000036E-3</v>
       </c>
       <c r="G2">
-        <v>4.0000000000000018E-3</v>
+        <v>1.0261333333333336E-2</v>
       </c>
       <c r="H2">
-        <v>4.0000000000000018E-3</v>
+        <v>1.2672000000000003E-2</v>
       </c>
       <c r="I2">
-        <v>4.0000000000000018E-3</v>
+        <v>1.5232000000000002E-2</v>
       </c>
       <c r="J2">
-        <v>8.9706666666666685E-3</v>
+        <v>1.7941333333333337E-2</v>
       </c>
       <c r="K2">
-        <v>8.9706666666666685E-3</v>
+        <v>2.0800000000000003E-2</v>
       </c>
       <c r="L2">
-        <v>8.9706666666666685E-3</v>
+        <v>2.3808000000000003E-2</v>
       </c>
       <c r="M2">
-        <v>8.9706666666666685E-3</v>
+        <v>2.6965333333333334E-2</v>
       </c>
       <c r="N2">
-        <v>1.5136E-2</v>
+        <v>3.0272E-2</v>
       </c>
       <c r="O2">
-        <v>1.5136E-2</v>
+        <v>3.3728000000000001E-2</v>
       </c>
       <c r="P2">
-        <v>1.5136E-2</v>
+        <v>3.7333333333333329E-2</v>
       </c>
       <c r="Q2">
-        <v>1.5136E-2</v>
+        <v>4.1088E-2</v>
       </c>
       <c r="R2">
-        <v>2.2495999999999999E-2</v>
+        <v>4.4991999999999997E-2</v>
       </c>
       <c r="S2">
-        <v>2.2495999999999999E-2</v>
+        <v>4.904533333333333E-2</v>
       </c>
       <c r="T2">
-        <v>2.2495999999999999E-2</v>
+        <v>5.3247999999999997E-2</v>
       </c>
       <c r="U2">
-        <v>2.2495999999999999E-2</v>
+        <v>5.7599999999999998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -620,52 +620,52 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2.5500000000000028E-3</v>
+        <v>5.1000000000000056E-3</v>
       </c>
       <c r="G4">
-        <v>2.5500000000000028E-3</v>
+        <v>8.5924444444444512E-3</v>
       </c>
       <c r="H4">
-        <v>2.5500000000000028E-3</v>
+        <v>1.2963111111111118E-2</v>
       </c>
       <c r="I4">
-        <v>2.5500000000000028E-3</v>
+        <v>1.8212000000000006E-2</v>
       </c>
       <c r="J4">
-        <v>1.2169555555555558E-2</v>
+        <v>2.4339111111111117E-2</v>
       </c>
       <c r="K4">
-        <v>1.2169555555555558E-2</v>
+        <v>3.1344444444444446E-2</v>
       </c>
       <c r="L4">
-        <v>1.2169555555555558E-2</v>
+        <v>3.9227999999999999E-2</v>
       </c>
       <c r="M4">
-        <v>1.2169555555555558E-2</v>
+        <v>4.7989777777777784E-2</v>
       </c>
       <c r="N4">
-        <v>2.8814888888888886E-2</v>
+        <v>5.7629777777777773E-2</v>
       </c>
       <c r="O4">
-        <v>2.8814888888888886E-2</v>
+        <v>6.8148E-2</v>
       </c>
       <c r="P4">
-        <v>2.8814888888888886E-2</v>
+        <v>7.9544444444444445E-2</v>
       </c>
       <c r="Q4">
-        <v>2.8814888888888886E-2</v>
+        <v>9.1819111111111101E-2</v>
       </c>
       <c r="R4">
-        <v>5.2485999999999998E-2</v>
+        <v>0.104972</v>
       </c>
       <c r="S4">
-        <v>5.2485999999999998E-2</v>
+        <v>0.1190031111111111</v>
       </c>
       <c r="T4">
-        <v>5.2485999999999998E-2</v>
+        <v>0.13391244444444442</v>
       </c>
       <c r="U4">
-        <v>5.2485999999999998E-2</v>
+        <v>0.14969999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -685,52 +685,52 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3.5999999999999999E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="G5">
-        <v>3.5999999999999999E-3</v>
+        <v>1.1576888888888888E-2</v>
       </c>
       <c r="H5">
-        <v>3.5999999999999999E-3</v>
+        <v>1.6974222222222224E-2</v>
       </c>
       <c r="I5">
-        <v>3.5999999999999999E-3</v>
+        <v>2.3392E-2</v>
       </c>
       <c r="J5">
-        <v>1.541511111111111E-2</v>
+        <v>3.0830222222222221E-2</v>
       </c>
       <c r="K5">
-        <v>1.541511111111111E-2</v>
+        <v>3.9288888888888887E-2</v>
       </c>
       <c r="L5">
-        <v>1.541511111111111E-2</v>
+        <v>4.8767999999999999E-2</v>
       </c>
       <c r="M5">
-        <v>1.541511111111111E-2</v>
+        <v>5.9267555555555552E-2</v>
       </c>
       <c r="N5">
-        <v>3.5393777777777774E-2</v>
+        <v>7.0787555555555548E-2</v>
       </c>
       <c r="O5">
-        <v>3.5393777777777774E-2</v>
+        <v>8.3327999999999985E-2</v>
       </c>
       <c r="P5">
-        <v>3.5393777777777774E-2</v>
+        <v>9.6888888888888886E-2</v>
       </c>
       <c r="Q5">
-        <v>3.5393777777777774E-2</v>
+        <v>0.11147022222222222</v>
       </c>
       <c r="R5">
-        <v>6.3535999999999995E-2</v>
+        <v>0.12707199999999999</v>
       </c>
       <c r="S5">
-        <v>6.3535999999999995E-2</v>
+        <v>0.14369422222222222</v>
       </c>
       <c r="T5">
-        <v>6.3535999999999995E-2</v>
+        <v>0.16133688888888889</v>
       </c>
       <c r="U5">
-        <v>6.3535999999999995E-2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -750,52 +750,52 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3.9809533183954061E-3</v>
+        <v>7.9619066367908123E-3</v>
       </c>
       <c r="G6">
-        <v>3.9809533183954061E-3</v>
+        <v>1.2473839090245582E-2</v>
       </c>
       <c r="H6">
-        <v>3.9809533183954061E-3</v>
+        <v>1.7911096368094518E-2</v>
       </c>
       <c r="I6">
-        <v>3.9809533183954061E-3</v>
+        <v>2.4273678470337626E-2</v>
       </c>
       <c r="J6">
-        <v>1.5780792698487447E-2</v>
+        <v>3.1561585396974894E-2</v>
       </c>
       <c r="K6">
-        <v>1.5780792698487447E-2</v>
+        <v>3.977481714800634E-2</v>
       </c>
       <c r="L6">
-        <v>1.5780792698487447E-2</v>
+        <v>4.8913373723431949E-2</v>
       </c>
       <c r="M6">
-        <v>1.5780792698487447E-2</v>
+        <v>5.8977255123251714E-2</v>
       </c>
       <c r="N6">
-        <v>3.4983230673732831E-2</v>
+        <v>6.9966461347465661E-2</v>
       </c>
       <c r="O6">
-        <v>3.4983230673732831E-2</v>
+        <v>8.1880992396073785E-2</v>
       </c>
       <c r="P6">
-        <v>3.4983230673732831E-2</v>
+        <v>9.4720848269076063E-2</v>
       </c>
       <c r="Q6">
-        <v>3.4983230673732831E-2</v>
+        <v>0.1084860289664725</v>
       </c>
       <c r="R6">
-        <v>6.1588267244131557E-2</v>
+        <v>0.12317653448826311</v>
       </c>
       <c r="S6">
-        <v>6.1588267244131557E-2</v>
+        <v>0.13879236483444787</v>
       </c>
       <c r="T6">
-        <v>6.1588267244131557E-2</v>
+        <v>0.15533352000502687</v>
       </c>
       <c r="U6">
-        <v>6.1588267244131557E-2</v>
+        <v>0.17279999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -1010,52 +1010,52 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>3.2000000000000015E-3</v>
+        <v>7.9999999999999988E-2</v>
       </c>
       <c r="G10">
-        <v>4.100266666666668E-3</v>
+        <v>8.5999999999999979E-2</v>
       </c>
       <c r="H10">
-        <v>5.0005333333333355E-3</v>
+        <v>9.1999999999999985E-2</v>
       </c>
       <c r="I10">
-        <v>5.9008000000000021E-3</v>
+        <v>9.799999999999999E-2</v>
       </c>
       <c r="J10">
-        <v>6.8010666666666686E-3</v>
+        <v>0.10399999999999998</v>
       </c>
       <c r="K10">
-        <v>7.7013333333333361E-3</v>
+        <v>0.10999999999999999</v>
       </c>
       <c r="L10">
-        <v>8.6016000000000026E-3</v>
+        <v>0.11599999999999999</v>
       </c>
       <c r="M10">
-        <v>9.5018666666666692E-3</v>
+        <v>0.122</v>
       </c>
       <c r="N10">
-        <v>1.0402133333333336E-2</v>
+        <v>0.128</v>
       </c>
       <c r="O10">
-        <v>1.1302400000000002E-2</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="P10">
-        <v>1.2202666666666669E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q10">
-        <v>1.3102933333333337E-2</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="R10">
-        <v>1.4003200000000004E-2</v>
+        <v>0.152</v>
       </c>
       <c r="S10">
-        <v>1.490346666666667E-2</v>
+        <v>0.158</v>
       </c>
       <c r="T10">
-        <v>1.5803733333333337E-2</v>
+        <v>0.16399999999999998</v>
       </c>
       <c r="U10">
-        <v>1.6704000000000004E-2</v>
+        <v>0.16999999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
